--- a/data/gen-fc-typology-data-rev1.xlsx
+++ b/data/gen-fc-typology-data-rev1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10916"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kowk/Dropbox/GitHub/FCA-grammar-typology/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BBEFE6-20F3-B946-A4CB-F609A560E2DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93C79A0-0AC3-BF43-9E9C-B1B7D7F6A408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="32560" windowHeight="17140" tabRatio="730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5240" yWindow="500" windowWidth="32560" windowHeight="17140" tabRatio="730" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="typology.data28a" sheetId="3" r:id="rId1"/>
@@ -19459,7 +19459,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE55"/>
+  <dimension ref="A1:AE58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.375" defaultRowHeight="20" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.875" style="1" customWidth="1"/>
@@ -23391,6 +23391,86 @@
       <c r="AB55" s="11">
         <f>_xlfn.LET(_xlpm.a,AB$2:AB$22,_xlpm.b,$AB$2:$AB$22,CORREL(_xlpm.a,_xlpm.b))</f>
         <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="B58" s="1">
+        <v>1</v>
+      </c>
+      <c r="C58" s="1">
+        <v>2</v>
+      </c>
+      <c r="D58" s="1">
+        <v>3</v>
+      </c>
+      <c r="E58" s="1">
+        <v>4</v>
+      </c>
+      <c r="F58" s="1">
+        <v>5</v>
+      </c>
+      <c r="G58" s="1">
+        <v>6</v>
+      </c>
+      <c r="H58" s="1">
+        <v>7</v>
+      </c>
+      <c r="I58" s="1">
+        <v>8</v>
+      </c>
+      <c r="J58" s="1">
+        <v>9</v>
+      </c>
+      <c r="K58" s="1">
+        <v>10</v>
+      </c>
+      <c r="L58" s="1">
+        <v>11</v>
+      </c>
+      <c r="M58" s="1">
+        <v>12</v>
+      </c>
+      <c r="N58" s="1">
+        <v>13</v>
+      </c>
+      <c r="O58" s="1">
+        <v>14</v>
+      </c>
+      <c r="P58" s="1">
+        <v>15</v>
+      </c>
+      <c r="Q58" s="1">
+        <v>16</v>
+      </c>
+      <c r="R58" s="1">
+        <v>17</v>
+      </c>
+      <c r="S58" s="1">
+        <v>18</v>
+      </c>
+      <c r="T58" s="1">
+        <v>19</v>
+      </c>
+      <c r="U58" s="1">
+        <v>20</v>
+      </c>
+      <c r="V58" s="1">
+        <v>21</v>
+      </c>
+      <c r="W58" s="1">
+        <v>22</v>
+      </c>
+      <c r="X58" s="1">
+        <v>23</v>
+      </c>
+      <c r="Y58" s="1">
+        <v>24</v>
+      </c>
+      <c r="Z58" s="1">
+        <v>25</v>
+      </c>
+      <c r="AA58" s="1">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
